--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,17 +434,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Space</t>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -456,26 +446,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.95038</v>
+        <v>17.39256</v>
       </c>
       <c r="D2" t="n">
-        <v>16.22384</v>
+        <v>17.05425</v>
       </c>
       <c r="E2" t="n">
-        <v>16.91754</v>
+        <v>17.16965</v>
       </c>
       <c r="F2" t="n">
-        <v>22.00928</v>
+        <v>44.09887</v>
       </c>
       <c r="G2" t="n">
-        <v>22.14486</v>
+        <v>0.05135</v>
       </c>
       <c r="H2" t="n">
-        <v>35.05681</v>
+        <v>1.86771</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +475,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.2413</v>
+        <v>17.19825</v>
       </c>
       <c r="D3" t="n">
-        <v>16.72643</v>
+        <v>16.94008</v>
       </c>
       <c r="E3" t="n">
-        <v>17.01761</v>
+        <v>17.06511</v>
       </c>
       <c r="F3" t="n">
-        <v>22.32722</v>
+        <v>43.01496</v>
       </c>
       <c r="G3" t="n">
-        <v>22.43012</v>
+        <v>0.05152</v>
       </c>
       <c r="H3" t="n">
-        <v>34.84909</v>
+        <v>1.85495</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +500,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.09938</v>
+        <v>17.41279</v>
       </c>
       <c r="D4" t="n">
-        <v>16.68795</v>
+        <v>17.09713</v>
       </c>
       <c r="E4" t="n">
-        <v>16.46712</v>
+        <v>17.22183</v>
       </c>
       <c r="F4" t="n">
-        <v>22.82045</v>
+        <v>44.38171</v>
       </c>
       <c r="G4" t="n">
-        <v>22.73687</v>
+        <v>0.05214</v>
       </c>
       <c r="H4" t="n">
-        <v>34.98153</v>
+        <v>1.90418</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +525,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.21055</v>
+        <v>17.45923</v>
       </c>
       <c r="D5" t="n">
-        <v>16.61616</v>
+        <v>16.8354</v>
       </c>
       <c r="E5" t="n">
-        <v>16.90076</v>
+        <v>16.92791</v>
       </c>
       <c r="F5" t="n">
-        <v>22.10826</v>
+        <v>43.5702</v>
       </c>
       <c r="G5" t="n">
-        <v>22.72367</v>
+        <v>0.0516</v>
       </c>
       <c r="H5" t="n">
-        <v>35.66613</v>
+        <v>1.83357</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +550,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.24718</v>
+        <v>17.63861</v>
       </c>
       <c r="D6" t="n">
-        <v>16.72462</v>
+        <v>16.98134</v>
       </c>
       <c r="E6" t="n">
-        <v>16.74585</v>
+        <v>17.30393</v>
       </c>
       <c r="F6" t="n">
-        <v>22.74204</v>
+        <v>44.39984</v>
       </c>
       <c r="G6" t="n">
-        <v>22.80544</v>
+        <v>0.05228</v>
       </c>
       <c r="H6" t="n">
-        <v>35.13319</v>
+        <v>1.87128</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +575,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.34988</v>
+        <v>17.30835</v>
       </c>
       <c r="D7" t="n">
-        <v>16.24279</v>
+        <v>16.90493</v>
       </c>
       <c r="E7" t="n">
-        <v>16.88916</v>
+        <v>17.06674</v>
       </c>
       <c r="F7" t="n">
-        <v>22.00206</v>
+        <v>43.70941</v>
       </c>
       <c r="G7" t="n">
-        <v>22.67105</v>
+        <v>0.05207</v>
       </c>
       <c r="H7" t="n">
-        <v>35.65779</v>
+        <v>1.87599</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +600,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.9796</v>
+        <v>17.2459</v>
       </c>
       <c r="D8" t="n">
-        <v>16.08944</v>
+        <v>16.82288</v>
       </c>
       <c r="E8" t="n">
-        <v>17.2053</v>
+        <v>17.01839</v>
       </c>
       <c r="F8" t="n">
-        <v>22.48504</v>
+        <v>43.23559</v>
       </c>
       <c r="G8" t="n">
-        <v>22.46694</v>
+        <v>0.0518</v>
       </c>
       <c r="H8" t="n">
-        <v>35.51725</v>
+        <v>1.90427</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +625,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.25034</v>
+        <v>17.33738</v>
       </c>
       <c r="D9" t="n">
-        <v>16.6422</v>
+        <v>16.53629</v>
       </c>
       <c r="E9" t="n">
-        <v>16.61374</v>
+        <v>16.9832</v>
       </c>
       <c r="F9" t="n">
-        <v>22.15014</v>
+        <v>44.12988</v>
       </c>
       <c r="G9" t="n">
-        <v>22.73146</v>
+        <v>0.05223</v>
       </c>
       <c r="H9" t="n">
-        <v>35.37192</v>
+        <v>1.83993</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +650,156 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.45556</v>
+        <v>17.6315</v>
       </c>
       <c r="D10" t="n">
-        <v>16.31181</v>
+        <v>17.15456</v>
       </c>
       <c r="E10" t="n">
-        <v>16.79438</v>
+        <v>17.24423</v>
       </c>
       <c r="F10" t="n">
-        <v>22.69376</v>
+        <v>43.84542</v>
       </c>
       <c r="G10" t="n">
-        <v>22.68596</v>
+        <v>0.052</v>
       </c>
       <c r="H10" t="n">
-        <v>34.12609</v>
+        <v>1.86243</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.63168</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.1333</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.63469</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.14448</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.62249</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.16166</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.64011</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.14242</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.63602</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.15449</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.63501</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.13464</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.63572</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.13604</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.60764</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.14787</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6211100000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.14543</v>
       </c>
     </row>
   </sheetData>
